--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="89">
   <si>
     <t>codigo_ibge_6</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>39</t>
   </si>
   <si>
     <t>SEM_EPI</t>
@@ -1011,7 +1017,7 @@
         <v>411690</v>
       </c>
       <c r="B2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C2">
         <v>9</v>
@@ -1029,13 +1035,13 @@
         <v>27142</v>
       </c>
       <c r="H2">
-        <v>372.1</v>
+        <v>386.9</v>
       </c>
       <c r="I2">
         <v>33.2</v>
       </c>
       <c r="J2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1267,16 +1273,16 @@
         <v>411520</v>
       </c>
       <c r="B10">
-        <v>907</v>
+        <v>931</v>
       </c>
       <c r="C10">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E10">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -1285,10 +1291,10 @@
         <v>429660</v>
       </c>
       <c r="H10">
-        <v>211.1</v>
+        <v>216.7</v>
       </c>
       <c r="I10">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="J10">
         <v>7.9</v>
@@ -1299,7 +1305,7 @@
         <v>412450</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1317,7 +1323,7 @@
         <v>6463</v>
       </c>
       <c r="H11">
-        <v>185.7</v>
+        <v>201.1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1427,7 +1433,7 @@
         <v>411480</v>
       </c>
       <c r="B15">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1436,7 +1442,7 @@
         <v>6</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
@@ -1445,13 +1451,13 @@
         <v>44749</v>
       </c>
       <c r="H15">
-        <v>138.6</v>
+        <v>143</v>
       </c>
       <c r="I15">
         <v>4.5</v>
       </c>
       <c r="J15">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1491,16 +1497,16 @@
         <v>412625</v>
       </c>
       <c r="B17">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C17">
         <v>8</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F17" t="s">
         <v>31</v>
@@ -1509,13 +1515,13 @@
         <v>128106</v>
       </c>
       <c r="H17">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I17">
         <v>6.2</v>
       </c>
       <c r="J17">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1552,28 +1558,28 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19">
-        <v>411360</v>
+        <v>410210</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>4707</v>
+        <v>26203</v>
       </c>
       <c r="H19">
-        <v>63.7</v>
+        <v>68.7</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1584,28 +1590,28 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20">
-        <v>410210</v>
+        <v>411360</v>
       </c>
       <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
         <v>15</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>4</v>
-      </c>
       <c r="G20">
-        <v>26203</v>
+        <v>4707</v>
       </c>
       <c r="H20">
-        <v>57.2</v>
+        <v>63.7</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1814,7 +1820,7 @@
         <v>14</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -1832,10 +1838,10 @@
         <v>36.5</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1909,7 +1915,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -1965,7 +1971,7 @@
         <v>48</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2101,7 +2107,7 @@
         <v>65</v>
       </c>
       <c r="B24">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2157,7 +2163,7 @@
         <v>72</v>
       </c>
       <c r="B31">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2205,7 +2211,23 @@
         <v>78</v>
       </c>
       <c r="B37">
-        <v>22</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>79</v>
+      </c>
+      <c r="B38">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2215,15 +2237,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>34</v>
@@ -2234,7 +2256,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -2245,7 +2267,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2256,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -2267,7 +2289,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -2278,7 +2300,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2289,7 +2311,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -2300,7 +2322,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -2311,7 +2333,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -2322,7 +2344,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2333,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -2344,7 +2366,7 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12">
         <v>14</v>
@@ -2355,7 +2377,7 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -2366,7 +2388,7 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2377,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -2388,7 +2410,7 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2399,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -2410,7 +2432,7 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -2421,7 +2443,7 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C19">
         <v>9</v>
@@ -2432,7 +2454,7 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2443,7 +2465,7 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -2454,7 +2476,7 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2465,10 +2487,10 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2476,7 +2498,7 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2487,7 +2509,7 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -2498,10 +2520,10 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2509,10 +2531,10 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2520,7 +2542,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -2531,7 +2553,7 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -2542,7 +2564,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -2553,7 +2575,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C31">
         <v>19</v>
@@ -2564,7 +2586,7 @@
         <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2575,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33">
         <v>4</v>
@@ -2586,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C34">
         <v>10</v>
@@ -2597,7 +2619,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -2608,7 +2630,7 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>4</v>
@@ -2619,7 +2641,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -2630,7 +2652,7 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38">
         <v>7</v>
@@ -2641,7 +2663,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C39">
         <v>15</v>
@@ -2652,7 +2674,7 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -2663,7 +2685,7 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -2674,7 +2696,7 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C42">
         <v>9</v>
@@ -2685,7 +2707,7 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C43">
         <v>16</v>
@@ -2696,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2707,7 +2729,7 @@
         <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -2718,7 +2740,7 @@
         <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C46">
         <v>9</v>
@@ -2729,7 +2751,7 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C47">
         <v>10</v>
@@ -2740,7 +2762,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -2751,7 +2773,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C49">
         <v>4</v>
@@ -2762,7 +2784,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C50">
         <v>11</v>
@@ -2773,7 +2795,7 @@
         <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C51">
         <v>10</v>
@@ -2784,7 +2806,7 @@
         <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -2795,7 +2817,7 @@
         <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C53">
         <v>12</v>
@@ -2806,7 +2828,7 @@
         <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C54">
         <v>11</v>
@@ -2817,7 +2839,7 @@
         <v>16</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -2828,7 +2850,7 @@
         <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C56">
         <v>13</v>
@@ -2839,10 +2861,10 @@
         <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2850,21 +2872,21 @@
         <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C58">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -2872,10 +2894,10 @@
         <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2883,10 +2905,10 @@
         <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C61">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2894,10 +2916,10 @@
         <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2905,21 +2927,21 @@
         <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
         <v>84</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2927,10 +2949,10 @@
         <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C65">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2941,29 +2963,29 @@
         <v>86</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B67" t="s">
         <v>83</v>
       </c>
       <c r="C67">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B68" t="s">
         <v>84</v>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -2971,10 +2993,10 @@
         <v>19</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -2982,32 +3004,32 @@
         <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C71">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -3015,32 +3037,32 @@
         <v>20</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C73">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B74" t="s">
         <v>83</v>
       </c>
       <c r="C74">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B75" t="s">
         <v>84</v>
       </c>
       <c r="C75">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -3048,10 +3070,10 @@
         <v>21</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -3059,32 +3081,32 @@
         <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C77">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C78">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C79">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -3092,10 +3114,10 @@
         <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C80">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -3106,29 +3128,29 @@
         <v>86</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C82">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C83">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -3136,10 +3158,10 @@
         <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C84">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -3150,15 +3172,15 @@
         <v>86</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C86">
         <v>24</v>
@@ -3166,13 +3188,13 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C87">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -3180,32 +3202,32 @@
         <v>24</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C88">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C89">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C90">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -3213,32 +3235,32 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C91">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B92" t="s">
         <v>83</v>
       </c>
       <c r="C92">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B93" t="s">
         <v>84</v>
       </c>
       <c r="C93">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -3246,10 +3268,10 @@
         <v>26</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -3257,18 +3279,18 @@
         <v>26</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C95">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C96">
         <v>17</v>
@@ -3276,13 +3298,13 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C97">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -3290,10 +3312,10 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C98">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -3304,29 +3326,29 @@
         <v>86</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B100" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C100">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C101">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3334,32 +3356,32 @@
         <v>28</v>
       </c>
       <c r="B102" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C102">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B103" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C103">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B104" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C104">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:3">
@@ -3367,7 +3389,7 @@
         <v>29</v>
       </c>
       <c r="B105" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C105">
         <v>23</v>
@@ -3381,29 +3403,29 @@
         <v>86</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B107" t="s">
         <v>83</v>
       </c>
       <c r="C107">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B108" t="s">
         <v>84</v>
       </c>
       <c r="C108">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -3411,10 +3433,10 @@
         <v>30</v>
       </c>
       <c r="B109" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -3422,32 +3444,32 @@
         <v>30</v>
       </c>
       <c r="B110" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C110">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B111" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C111">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B112" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C112">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3455,10 +3477,10 @@
         <v>31</v>
       </c>
       <c r="B113" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C113">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3469,29 +3491,29 @@
         <v>86</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B115" t="s">
         <v>83</v>
       </c>
       <c r="C115">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B116" t="s">
         <v>84</v>
       </c>
       <c r="C116">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3499,7 +3521,7 @@
         <v>32</v>
       </c>
       <c r="B117" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -3510,10 +3532,10 @@
         <v>32</v>
       </c>
       <c r="B118" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C118">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -3524,29 +3546,29 @@
         <v>86</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B120" t="s">
         <v>83</v>
       </c>
       <c r="C120">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B121" t="s">
         <v>84</v>
       </c>
       <c r="C121">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -3554,10 +3576,10 @@
         <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -3565,43 +3587,43 @@
         <v>33</v>
       </c>
       <c r="B123" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C123">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B124" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B125" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C125">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B126" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C126">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -3609,43 +3631,43 @@
         <v>34</v>
       </c>
       <c r="B127" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C127">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B128" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B129" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B130" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C130">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3653,51 +3675,51 @@
         <v>35</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C131">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B132" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C132">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B133" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B134" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C135">
         <v>10</v>
@@ -3708,7 +3730,7 @@
         <v>36</v>
       </c>
       <c r="B136" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C136">
         <v>8</v>
@@ -3716,68 +3738,123 @@
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B137" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C137">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B138" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C138">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B139" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C139">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B140" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C140">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B141" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C141">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B142" t="s">
+        <v>86</v>
+      </c>
+      <c r="C142">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143">
+        <v>39</v>
+      </c>
+      <c r="B143" t="s">
         <v>84</v>
       </c>
-      <c r="C142">
-        <v>2</v>
+      <c r="C143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144">
+        <v>39</v>
+      </c>
+      <c r="B144" t="s">
+        <v>88</v>
+      </c>
+      <c r="C144">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145">
+        <v>39</v>
+      </c>
+      <c r="B145" t="s">
+        <v>87</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146">
+        <v>39</v>
+      </c>
+      <c r="B146" t="s">
+        <v>85</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147">
+        <v>39</v>
+      </c>
+      <c r="B147" t="s">
+        <v>86</v>
+      </c>
+      <c r="C147">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="51">
   <si>
     <t>codigo_ibge_6</t>
   </si>
@@ -133,6 +133,9 @@
     <t>uti</t>
   </si>
   <si>
+    <t>encerrados</t>
+  </si>
+  <si>
     <t>incidencia_100k</t>
   </si>
   <si>
@@ -142,127 +145,10 @@
     <t>letalidade_pct</t>
   </si>
   <si>
-    <t>SEM_NOT</t>
+    <t>SEM_EPI</t>
   </si>
   <si>
     <t>total</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>SEM_EPI</t>
   </si>
   <si>
     <t>CLASSIFICACAO</t>
@@ -977,10 +863,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1">
+    <row r="1" spans="1:11" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -997,13 +883,13 @@
         <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>39</v>
@@ -1011,40 +897,46 @@
       <c r="J1" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>411690</v>
       </c>
       <c r="B2">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>101</v>
+      </c>
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>27142</v>
       </c>
-      <c r="H2">
-        <v>386.9</v>
-      </c>
       <c r="I2">
-        <v>33.2</v>
+        <v>420</v>
       </c>
       <c r="J2">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>36.8</v>
+      </c>
+      <c r="K2">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>412360</v>
       </c>
@@ -1060,23 +952,26 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1745</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>286.5</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>412830</v>
       </c>
@@ -1092,23 +987,26 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2106</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>284.9</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>47.5</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>16.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>411740</v>
       </c>
@@ -1124,188 +1022,206 @@
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5" t="s">
         <v>23</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>3193</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>250.5</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
       <c r="J5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
+        <v>410220</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4046</v>
+      </c>
+      <c r="I6">
+        <v>247.2</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>411090</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>4530</v>
+      </c>
+      <c r="I7">
+        <v>242.8</v>
+      </c>
+      <c r="J7">
+        <v>22.1</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
         <v>412530</v>
       </c>
-      <c r="B6">
+      <c r="B8">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>30</v>
       </c>
-      <c r="G6">
+      <c r="H8">
         <v>5170</v>
       </c>
-      <c r="H6">
+      <c r="I8">
         <v>232.1</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7">
-        <v>410220</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>4046</v>
-      </c>
-      <c r="H7">
-        <v>222.4</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8">
-        <v>411090</v>
-      </c>
-      <c r="B8">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>4530</v>
-      </c>
-      <c r="H8">
-        <v>220.8</v>
-      </c>
-      <c r="I8">
-        <v>22.1</v>
-      </c>
       <c r="J8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
+        <v>411520</v>
+      </c>
+      <c r="B9">
+        <v>970</v>
+      </c>
+      <c r="C9">
+        <v>81</v>
+      </c>
+      <c r="D9">
+        <v>55</v>
+      </c>
+      <c r="E9">
+        <v>287</v>
+      </c>
+      <c r="F9">
+        <v>862</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9">
+        <v>429660</v>
+      </c>
+      <c r="I9">
+        <v>225.8</v>
+      </c>
+      <c r="J9">
+        <v>18.9</v>
+      </c>
+      <c r="K9">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
         <v>411640</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>8</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s">
         <v>21</v>
       </c>
-      <c r="G9">
+      <c r="H10">
         <v>3669</v>
       </c>
-      <c r="H9">
+      <c r="I10">
         <v>218</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10">
-        <v>411520</v>
-      </c>
-      <c r="B10">
-        <v>931</v>
-      </c>
-      <c r="C10">
-        <v>74</v>
-      </c>
-      <c r="D10">
-        <v>51</v>
-      </c>
-      <c r="E10">
-        <v>269</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10">
-        <v>429660</v>
-      </c>
-      <c r="H10">
-        <v>216.7</v>
-      </c>
-      <c r="I10">
-        <v>17.2</v>
-      </c>
       <c r="J10">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>412450</v>
       </c>
       <c r="B11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1314,25 +1230,28 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>29</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>6463</v>
       </c>
-      <c r="H11">
-        <v>201.1</v>
-      </c>
       <c r="I11">
-        <v>0</v>
+        <v>216.6</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>410590</v>
       </c>
@@ -1348,92 +1267,101 @@
       <c r="E12">
         <v>2</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
         <v>6</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>23313</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>180.2</v>
       </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
       <c r="J12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
-        <v>410780</v>
+        <v>411110</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13">
         <v>8</v>
       </c>
-      <c r="G13">
-        <v>4805</v>
+      <c r="G13" t="s">
+        <v>13</v>
       </c>
       <c r="H13">
-        <v>145.7</v>
+        <v>6228</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>160.6</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
-        <v>411110</v>
+        <v>410780</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14">
-        <v>6228</v>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
       </c>
       <c r="H14">
-        <v>144.5</v>
+        <v>4805</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>145.7</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>411480</v>
       </c>
       <c r="B15">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1442,25 +1370,28 @@
         <v>6</v>
       </c>
       <c r="E15">
-        <v>30</v>
-      </c>
-      <c r="F15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15">
+        <v>64</v>
+      </c>
+      <c r="G15" t="s">
         <v>18</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>44749</v>
       </c>
-      <c r="H15">
-        <v>143</v>
-      </c>
       <c r="I15">
+        <v>145.3</v>
+      </c>
+      <c r="J15">
         <v>4.5</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>3.1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>411810</v>
       </c>
@@ -1476,55 +1407,61 @@
       <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
         <v>25</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>9549</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>104.7</v>
       </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
       <c r="J16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>412625</v>
       </c>
       <c r="B17">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>12</v>
       </c>
       <c r="E17">
-        <v>50</v>
-      </c>
-      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17">
+        <v>129</v>
+      </c>
+      <c r="G17" t="s">
         <v>31</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>128106</v>
       </c>
-      <c r="H17">
-        <v>98.40000000000001</v>
-      </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>103</v>
       </c>
       <c r="J17">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>7</v>
+      </c>
+      <c r="K17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>411630</v>
       </c>
@@ -1540,28 +1477,31 @@
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" t="s">
         <v>20</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>4057</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>73.90000000000001</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
       <c r="J18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>410210</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1572,23 +1512,26 @@
       <c r="E19">
         <v>5</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
         <v>4</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>26203</v>
       </c>
-      <c r="H19">
-        <v>68.7</v>
-      </c>
       <c r="I19">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>411360</v>
       </c>
@@ -1604,28 +1547,31 @@
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" t="s">
         <v>15</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>4707</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>63.7</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
       <c r="J20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>410790</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1634,25 +1580,28 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
         <v>9</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>11522</v>
       </c>
-      <c r="H21">
-        <v>52.1</v>
-      </c>
       <c r="I21">
-        <v>0</v>
+        <v>60.8</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>411750</v>
       </c>
@@ -1668,87 +1617,96 @@
       <c r="E22">
         <v>15</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22">
         <v>24</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22">
         <v>48695</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>49.3</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>2.1</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>4.2</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:11">
       <c r="A23">
+        <v>412040</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23">
+        <v>4304</v>
+      </c>
+      <c r="I23">
+        <v>46.5</v>
+      </c>
+      <c r="J23">
+        <v>23.2</v>
+      </c>
+      <c r="K23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24">
         <v>411410</v>
       </c>
-      <c r="B23">
-        <v>17</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
+      <c r="B24">
+        <v>16</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
         <v>7</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
         <v>16</v>
       </c>
-      <c r="G23">
+      <c r="H24">
         <v>34521</v>
       </c>
-      <c r="H23">
-        <v>49.2</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24">
-        <v>412040</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24">
-        <v>4304</v>
-      </c>
-      <c r="H24">
-        <v>46.5</v>
-      </c>
       <c r="I24">
-        <v>23.2</v>
+        <v>46.3</v>
       </c>
       <c r="J24">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>412340</v>
       </c>
@@ -1764,23 +1722,26 @@
       <c r="E25">
         <v>4</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25" t="s">
         <v>27</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>11730</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>42.6</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
       <c r="J25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>410810</v>
       </c>
@@ -1796,23 +1757,23 @@
       <c r="E26">
         <v>1</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
         <v>10</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>2711</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>36.9</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
       <c r="J26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>411420</v>
       </c>
@@ -1820,31 +1781,34 @@
         <v>14</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>11</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
         <v>17</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>38313</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>36.5</v>
       </c>
-      <c r="I27">
-        <v>2.6</v>
-      </c>
       <c r="J27">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>411000</v>
       </c>
@@ -1860,23 +1824,26 @@
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28" t="s">
         <v>11</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>5693</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>35.1</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
       <c r="J28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>410730</v>
       </c>
@@ -1892,19 +1859,22 @@
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
         <v>7</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>6517</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>30.7</v>
       </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
       <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
         <v>0</v>
       </c>
     </row>
@@ -1915,319 +1885,327 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>43</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>44</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>45</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>46</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>47</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>48</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>49</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>50</v>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="B9">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>51</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11">
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12">
+      <c r="B32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B15">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>76</v>
-      </c>
       <c r="B35">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>77</v>
+      <c r="A36">
+        <v>35</v>
       </c>
       <c r="B36">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
         <v>38</v>
       </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
       <c r="B39">
-        <v>23</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2237,15 +2215,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>34</v>
@@ -2253,54 +2231,54 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2308,57 +2286,57 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10">
         <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2366,62 +2344,62 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -2429,54 +2407,54 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18">
         <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C19">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2484,32 +2462,32 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -2517,505 +2495,505 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C26">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C31">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C39">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="C51">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C54">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C56">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C57">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="C58">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C60">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C62">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C64">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C65">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="C66">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C68">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C69">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C70">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C71">
         <v>9</v>
@@ -3023,175 +3001,175 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C72">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="C73">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C75">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C76">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C77">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="C78">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C80">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C81">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="C82">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C84">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C85">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C86">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C87">
         <v>21</v>
@@ -3199,274 +3177,274 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C88">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C89">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B90" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C90">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B91" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C91">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C93">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C94">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C95">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C96">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B97" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C98">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B99" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C99">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C100">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B101" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="C101">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="C102">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="C103">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B105" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C105">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B106" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C106">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B107" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B108" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C108">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B109" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C109">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B110" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C110">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B111" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C111">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B112" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -3474,54 +3452,54 @@
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B113" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C113">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B114" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C114">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B115" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B116" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C116">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B117" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -3529,189 +3507,189 @@
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B118" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C118">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B119" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C119">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B120" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B121" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C121">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B122" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C122">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B123" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C123">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C124">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B125" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B126" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C126">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B127" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B128" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C128">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B129" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C129">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B130" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C130">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B131" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C131">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B132" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C132">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B133" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B134" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -3719,10 +3697,10 @@
         <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C135">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3730,32 +3708,32 @@
         <v>36</v>
       </c>
       <c r="B136" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C136">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B137" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="C137">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B138" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="C138">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3763,76 +3741,76 @@
         <v>37</v>
       </c>
       <c r="B139" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C139">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B140" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C140">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B141" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="C141">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B142" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C142">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B143" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B144" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="C144">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B145" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -3840,10 +3818,10 @@
         <v>39</v>
       </c>
       <c r="B146" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3851,10 +3829,21 @@
         <v>39</v>
       </c>
       <c r="B147" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>39</v>
+      </c>
+      <c r="B148" t="s">
+        <v>48</v>
+      </c>
+      <c r="C148">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -909,7 +909,7 @@
         <v>114</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -918,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -930,10 +930,10 @@
         <v>420</v>
       </c>
       <c r="J2">
-        <v>36.8</v>
+        <v>40.5</v>
       </c>
       <c r="K2">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>411740</v>
+        <v>410220</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1020,19 +1020,19 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>3193</v>
+        <v>4046</v>
       </c>
       <c r="I5">
-        <v>250.5</v>
+        <v>271.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6">
-        <v>410220</v>
+        <v>411740</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1055,19 +1055,19 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H6">
-        <v>4046</v>
+        <v>3193</v>
       </c>
       <c r="I6">
-        <v>247.2</v>
+        <v>250.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1151,19 +1151,19 @@
         <v>411520</v>
       </c>
       <c r="B9">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="C9">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9">
         <v>55</v>
       </c>
       <c r="E9">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F9">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1172,13 +1172,13 @@
         <v>429660</v>
       </c>
       <c r="I9">
-        <v>225.8</v>
+        <v>227.4</v>
       </c>
       <c r="J9">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="K9">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1256,7 +1256,7 @@
         <v>410590</v>
       </c>
       <c r="B12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>23313</v>
       </c>
       <c r="I12">
-        <v>180.2</v>
+        <v>184.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1431,7 +1431,7 @@
         <v>412625</v>
       </c>
       <c r="B17">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C17">
         <v>9</v>
@@ -1443,7 +1443,7 @@
         <v>52</v>
       </c>
       <c r="F17">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G17" t="s">
         <v>31</v>
@@ -1452,13 +1452,13 @@
         <v>128106</v>
       </c>
       <c r="I17">
-        <v>103</v>
+        <v>104.6</v>
       </c>
       <c r="J17">
         <v>7</v>
       </c>
       <c r="K17">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1638,72 +1638,72 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>412040</v>
+        <v>411410</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H23">
-        <v>4304</v>
+        <v>34521</v>
       </c>
       <c r="I23">
-        <v>46.5</v>
+        <v>49.2</v>
       </c>
       <c r="J23">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>411410</v>
+        <v>412040</v>
       </c>
       <c r="B24">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H24">
-        <v>34521</v>
+        <v>4304</v>
       </c>
       <c r="I24">
-        <v>46.3</v>
+        <v>46.5</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1743,68 +1743,68 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>410810</v>
+        <v>411420</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H26">
-        <v>2711</v>
+        <v>38313</v>
       </c>
       <c r="I26">
-        <v>36.9</v>
+        <v>39.2</v>
       </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>411420</v>
+        <v>410810</v>
       </c>
       <c r="B27">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>38313</v>
+        <v>2711</v>
       </c>
       <c r="I27">
-        <v>36.5</v>
+        <v>36.9</v>
       </c>
       <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
         <v>0</v>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2085,7 +2085,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2205,7 +2205,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3172,7 +3172,7 @@
         <v>46</v>
       </c>
       <c r="C87">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -3205,7 +3205,7 @@
         <v>46</v>
       </c>
       <c r="C90">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -3744,7 +3744,7 @@
         <v>50</v>
       </c>
       <c r="C139">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3766,7 +3766,7 @@
         <v>47</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -3777,7 +3777,7 @@
         <v>48</v>
       </c>
       <c r="C142">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -3788,7 +3788,7 @@
         <v>50</v>
       </c>
       <c r="C143">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -3799,7 +3799,7 @@
         <v>47</v>
       </c>
       <c r="C144">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -3810,7 +3810,7 @@
         <v>48</v>
       </c>
       <c r="C145">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -3821,7 +3821,7 @@
         <v>50</v>
       </c>
       <c r="C146">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3832,7 +3832,7 @@
         <v>47</v>
       </c>
       <c r="C147">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -3843,7 +3843,7 @@
         <v>48</v>
       </c>
       <c r="C148">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="51">
   <si>
     <t>codigo_ibge_6</t>
   </si>
@@ -906,7 +906,7 @@
         <v>411690</v>
       </c>
       <c r="B2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C2">
         <v>11</v>
@@ -927,7 +927,7 @@
         <v>27142</v>
       </c>
       <c r="I2">
-        <v>420</v>
+        <v>427.4</v>
       </c>
       <c r="J2">
         <v>40.5</v>
@@ -1151,19 +1151,19 @@
         <v>411520</v>
       </c>
       <c r="B9">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C9">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9">
         <v>55</v>
       </c>
       <c r="E9">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F9">
-        <v>883</v>
+        <v>909</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1172,13 +1172,13 @@
         <v>429660</v>
       </c>
       <c r="I9">
-        <v>227.4</v>
+        <v>227.9</v>
       </c>
       <c r="J9">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="K9">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1393,72 +1393,72 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>411810</v>
+        <v>412625</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H16">
-        <v>9549</v>
+        <v>128106</v>
       </c>
       <c r="I16">
-        <v>104.7</v>
+        <v>105.4</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>412625</v>
+        <v>411810</v>
       </c>
       <c r="B17">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>130</v>
+        <v>10</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H17">
-        <v>128106</v>
+        <v>9549</v>
       </c>
       <c r="I17">
-        <v>104.6</v>
+        <v>104.7</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1885,7 +1885,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -2205,7 +2205,15 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>29</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2215,7 +2223,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:C150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -3216,7 +3224,7 @@
         <v>47</v>
       </c>
       <c r="C91">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -3227,7 +3235,7 @@
         <v>48</v>
       </c>
       <c r="C92">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -3821,7 +3829,7 @@
         <v>50</v>
       </c>
       <c r="C146">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3844,6 +3852,28 @@
       </c>
       <c r="C148">
         <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149">
+        <v>40</v>
+      </c>
+      <c r="B149" t="s">
+        <v>47</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>40</v>
+      </c>
+      <c r="B150" t="s">
+        <v>48</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -909,7 +909,7 @@
         <v>116</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -918,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -930,39 +930,39 @@
         <v>427.4</v>
       </c>
       <c r="J2">
-        <v>40.5</v>
+        <v>44.2</v>
       </c>
       <c r="K2">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3">
-        <v>412360</v>
+        <v>410220</v>
       </c>
       <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
       <c r="H3">
-        <v>1745</v>
+        <v>4046</v>
       </c>
       <c r="I3">
-        <v>286.5</v>
+        <v>296.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -973,13 +973,13 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4">
-        <v>412830</v>
+        <v>412360</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -988,57 +988,57 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>2106</v>
+        <v>1745</v>
       </c>
       <c r="I4">
-        <v>284.9</v>
+        <v>286.5</v>
       </c>
       <c r="J4">
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5">
-        <v>410220</v>
+        <v>412830</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H5">
-        <v>4046</v>
+        <v>2106</v>
       </c>
       <c r="I5">
-        <v>271.9</v>
+        <v>284.9</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1151,19 +1151,19 @@
         <v>411520</v>
       </c>
       <c r="B9">
-        <v>979</v>
+        <v>945</v>
       </c>
       <c r="C9">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="F9">
-        <v>909</v>
+        <v>867</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1172,13 +1172,13 @@
         <v>429660</v>
       </c>
       <c r="I9">
-        <v>227.9</v>
+        <v>219.9</v>
       </c>
       <c r="J9">
-        <v>19.6</v>
+        <v>18.2</v>
       </c>
       <c r="K9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1256,7 +1256,7 @@
         <v>410590</v>
       </c>
       <c r="B12">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>23313</v>
       </c>
       <c r="I12">
-        <v>184.4</v>
+        <v>188.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1396,19 +1396,19 @@
         <v>412625</v>
       </c>
       <c r="B16">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>12</v>
       </c>
       <c r="E16">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F16">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G16" t="s">
         <v>31</v>
@@ -1417,13 +1417,13 @@
         <v>128106</v>
       </c>
       <c r="I16">
-        <v>105.4</v>
+        <v>109.3</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="K16">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1504,10 +1504,10 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -1525,10 +1525,10 @@
         <v>72.5</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>411750</v>
+        <v>411410</v>
       </c>
       <c r="B22">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1615,60 +1615,60 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G22" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H22">
-        <v>48695</v>
+        <v>34521</v>
       </c>
       <c r="I22">
-        <v>49.3</v>
+        <v>52.1</v>
       </c>
       <c r="J22">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>411410</v>
+        <v>411750</v>
       </c>
       <c r="B23">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H23">
-        <v>34521</v>
+        <v>48695</v>
       </c>
       <c r="I23">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1901,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1925,7 +1925,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1933,7 +1933,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1949,7 +1949,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1965,7 +1965,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1989,7 +1989,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1997,7 +1997,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2005,7 +2005,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2013,7 +2013,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2021,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2029,7 +2029,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2045,7 +2045,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2053,7 +2053,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2061,7 +2061,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2069,7 +2069,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2077,7 +2077,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2085,7 +2085,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2093,7 +2093,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2109,7 +2109,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2117,7 +2117,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2133,7 +2133,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2157,7 +2157,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2197,7 +2197,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2205,7 +2205,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2213,7 +2213,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2245,7 +2245,7 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2366,7 +2366,7 @@
         <v>46</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2432,7 +2432,7 @@
         <v>48</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2520,7 +2520,7 @@
         <v>48</v>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -2597,7 +2597,7 @@
         <v>46</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -2608,7 +2608,7 @@
         <v>47</v>
       </c>
       <c r="C35">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -2619,7 +2619,7 @@
         <v>48</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -2751,7 +2751,7 @@
         <v>48</v>
       </c>
       <c r="C48">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -2770,10 +2770,10 @@
         <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -2781,21 +2781,21 @@
         <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C51">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C52">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -2803,10 +2803,10 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C53">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -2814,10 +2814,10 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -2825,21 +2825,21 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C56">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -2847,10 +2847,10 @@
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -2858,10 +2858,10 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C58">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -2869,7 +2869,7 @@
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C59">
         <v>14</v>
@@ -2877,13 +2877,13 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C60">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -2891,10 +2891,10 @@
         <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C61">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2902,10 +2902,10 @@
         <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -2913,21 +2913,21 @@
         <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C64">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2935,10 +2935,10 @@
         <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2946,10 +2946,10 @@
         <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -2957,21 +2957,21 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C67">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C68">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -2979,10 +2979,10 @@
         <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C69">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -2990,21 +2990,21 @@
         <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C70">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C71">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -3012,10 +3012,10 @@
         <v>19</v>
       </c>
       <c r="B72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -3023,10 +3023,10 @@
         <v>19</v>
       </c>
       <c r="B73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C73">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -3034,21 +3034,21 @@
         <v>19</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C74">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C75">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -3056,10 +3056,10 @@
         <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C76">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -3067,10 +3067,10 @@
         <v>20</v>
       </c>
       <c r="B77" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -3078,21 +3078,21 @@
         <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C78">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C79">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -3100,10 +3100,10 @@
         <v>21</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C80">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -3111,10 +3111,10 @@
         <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -3122,21 +3122,21 @@
         <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C82">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C83">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -3144,10 +3144,10 @@
         <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C84">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -3155,18 +3155,18 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C85">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B86" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C86">
         <v>16</v>
@@ -3177,10 +3177,10 @@
         <v>23</v>
       </c>
       <c r="B87" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C87">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -3188,7 +3188,7 @@
         <v>23</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C88">
         <v>17</v>
@@ -3196,13 +3196,13 @@
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C89">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -3210,10 +3210,10 @@
         <v>24</v>
       </c>
       <c r="B90" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C90">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -3221,21 +3221,21 @@
         <v>24</v>
       </c>
       <c r="B91" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C91">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C92">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -3243,10 +3243,10 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -3254,10 +3254,10 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C94">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -3265,21 +3265,21 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C95">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C96">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -3287,10 +3287,10 @@
         <v>26</v>
       </c>
       <c r="B97" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C97">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -3298,10 +3298,10 @@
         <v>26</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -3309,21 +3309,21 @@
         <v>26</v>
       </c>
       <c r="B99" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C99">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C100">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -3331,10 +3331,10 @@
         <v>27</v>
       </c>
       <c r="B101" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3342,7 +3342,7 @@
         <v>27</v>
       </c>
       <c r="B102" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C102">
         <v>24</v>
@@ -3353,18 +3353,18 @@
         <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C103">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B104" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C104">
         <v>19</v>
@@ -3375,10 +3375,10 @@
         <v>28</v>
       </c>
       <c r="B105" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C105">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:3">
@@ -3386,21 +3386,21 @@
         <v>28</v>
       </c>
       <c r="B106" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C106">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B107" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C107">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -3408,10 +3408,10 @@
         <v>29</v>
       </c>
       <c r="B108" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C108">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -3419,10 +3419,10 @@
         <v>29</v>
       </c>
       <c r="B109" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -3430,21 +3430,21 @@
         <v>29</v>
       </c>
       <c r="B110" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C110">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B111" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C111">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -3452,10 +3452,10 @@
         <v>30</v>
       </c>
       <c r="B112" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3463,10 +3463,10 @@
         <v>30</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C113">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3474,10 +3474,10 @@
         <v>30</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -3485,21 +3485,21 @@
         <v>30</v>
       </c>
       <c r="B115" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C115">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C116">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3507,10 +3507,10 @@
         <v>31</v>
       </c>
       <c r="B117" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:3">
@@ -3518,7 +3518,7 @@
         <v>31</v>
       </c>
       <c r="B118" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C118">
         <v>8</v>
@@ -3529,21 +3529,21 @@
         <v>31</v>
       </c>
       <c r="B119" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C119">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B120" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C120">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3551,10 +3551,10 @@
         <v>32</v>
       </c>
       <c r="B121" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C121">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -3562,21 +3562,21 @@
         <v>32</v>
       </c>
       <c r="B122" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C122">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B123" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C123">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -3584,10 +3584,10 @@
         <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C124">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3595,10 +3595,10 @@
         <v>33</v>
       </c>
       <c r="B125" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -3606,21 +3606,21 @@
         <v>33</v>
       </c>
       <c r="B126" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C126">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B127" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C127">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -3628,10 +3628,10 @@
         <v>34</v>
       </c>
       <c r="B128" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C128">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3639,10 +3639,10 @@
         <v>34</v>
       </c>
       <c r="B129" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3650,18 +3650,18 @@
         <v>34</v>
       </c>
       <c r="B130" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C130">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B131" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C131">
         <v>14</v>
@@ -3672,10 +3672,10 @@
         <v>35</v>
       </c>
       <c r="B132" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C132">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3683,21 +3683,21 @@
         <v>35</v>
       </c>
       <c r="B133" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B134" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C134">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -3705,10 +3705,10 @@
         <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C135">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3716,7 +3716,7 @@
         <v>36</v>
       </c>
       <c r="B136" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -3727,21 +3727,21 @@
         <v>36</v>
       </c>
       <c r="B137" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B138" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C138">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3749,10 +3749,10 @@
         <v>37</v>
       </c>
       <c r="B139" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C139">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3760,10 +3760,10 @@
         <v>37</v>
       </c>
       <c r="B140" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3771,21 +3771,21 @@
         <v>37</v>
       </c>
       <c r="B141" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C141">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C142">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -3793,10 +3793,10 @@
         <v>38</v>
       </c>
       <c r="B143" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C143">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -3804,7 +3804,7 @@
         <v>38</v>
       </c>
       <c r="B144" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C144">
         <v>11</v>
@@ -3812,13 +3812,13 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B145" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C145">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -3826,10 +3826,10 @@
         <v>39</v>
       </c>
       <c r="B146" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C146">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3837,21 +3837,21 @@
         <v>39</v>
       </c>
       <c r="B147" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B148" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C148">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -3862,7 +3862,7 @@
         <v>47</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -3873,7 +3873,7 @@
         <v>48</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="51">
   <si>
     <t>codigo_ibge_6</t>
   </si>
@@ -863,7 +863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1">
@@ -918,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="F2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -933,7 +933,7 @@
         <v>44.2</v>
       </c>
       <c r="K2">
-        <v>11.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -941,7 +941,7 @@
         <v>410220</v>
       </c>
       <c r="B3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -953,7 +953,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>5</v>
@@ -962,7 +962,7 @@
         <v>4046</v>
       </c>
       <c r="I3">
-        <v>296.6</v>
+        <v>321.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -1000,10 +1000,10 @@
         <v>286.5</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>57.3</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1093,7 +1093,7 @@
         <v>1</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -1108,7 +1108,7 @@
         <v>22.1</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1151,10 +1151,10 @@
         <v>411520</v>
       </c>
       <c r="B9">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="C9">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>56</v>
@@ -1163,7 +1163,7 @@
         <v>281</v>
       </c>
       <c r="F9">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1172,13 +1172,13 @@
         <v>429660</v>
       </c>
       <c r="I9">
-        <v>219.9</v>
+        <v>220.9</v>
       </c>
       <c r="J9">
-        <v>18.2</v>
+        <v>18.6</v>
       </c>
       <c r="K9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1233,7 +1233,7 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
@@ -1268,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="F12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
         <v>6</v>
@@ -1370,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <v>64</v>
@@ -1396,7 +1396,7 @@
         <v>412625</v>
       </c>
       <c r="B16">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C16">
         <v>10</v>
@@ -1405,10 +1405,10 @@
         <v>12</v>
       </c>
       <c r="E16">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F16">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16" t="s">
         <v>31</v>
@@ -1417,13 +1417,13 @@
         <v>128106</v>
       </c>
       <c r="I16">
-        <v>109.3</v>
+        <v>110.1</v>
       </c>
       <c r="J16">
         <v>7.8</v>
       </c>
       <c r="K16">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1513,7 +1513,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" t="s">
         <v>4</v>
@@ -1528,7 +1528,7 @@
         <v>3.8</v>
       </c>
       <c r="K19">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1875,6 +1875,38 @@
         <v>0</v>
       </c>
       <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30">
+        <v>410115</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>3357</v>
+      </c>
+      <c r="I30">
+        <v>29.8</v>
+      </c>
+      <c r="J30">
         <v>0</v>
       </c>
     </row>
@@ -1885,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -2189,7 +2221,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -2197,7 +2229,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2205,7 +2237,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2213,7 +2245,15 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>12</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2223,7 +2263,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -3587,7 +3627,7 @@
         <v>50</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3598,7 +3638,7 @@
         <v>47</v>
       </c>
       <c r="C125">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -3741,7 +3781,7 @@
         <v>50</v>
       </c>
       <c r="C138">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3749,10 +3789,10 @@
         <v>37</v>
       </c>
       <c r="B139" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3760,21 +3800,21 @@
         <v>37</v>
       </c>
       <c r="B140" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C140">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B141" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C141">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -3782,7 +3822,7 @@
         <v>38</v>
       </c>
       <c r="B142" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C142">
         <v>14</v>
@@ -3793,21 +3833,21 @@
         <v>38</v>
       </c>
       <c r="B143" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C143">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B144" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C144">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -3815,10 +3855,10 @@
         <v>39</v>
       </c>
       <c r="B145" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C145">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -3826,21 +3866,21 @@
         <v>39</v>
       </c>
       <c r="B146" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C146">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B147" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C147">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -3848,10 +3888,10 @@
         <v>40</v>
       </c>
       <c r="B148" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C148">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -3859,21 +3899,32 @@
         <v>40</v>
       </c>
       <c r="B149" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C149">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B150" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C150">
-        <v>4</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>41</v>
+      </c>
+      <c r="B151" t="s">
+        <v>48</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -1163,7 +1163,7 @@
         <v>281</v>
       </c>
       <c r="F9">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1178,7 +1178,7 @@
         <v>18.6</v>
       </c>
       <c r="K9">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="10" spans="1:11">

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="51">
   <si>
     <t>codigo_ibge_6</t>
   </si>
@@ -906,7 +906,7 @@
         <v>411690</v>
       </c>
       <c r="B2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2">
         <v>12</v>
@@ -915,10 +915,10 @@
         <v>2</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -927,13 +927,13 @@
         <v>27142</v>
       </c>
       <c r="I2">
-        <v>427.4</v>
+        <v>431.1</v>
       </c>
       <c r="J2">
         <v>44.2</v>
       </c>
       <c r="K2">
-        <v>11</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1151,19 +1151,19 @@
         <v>411520</v>
       </c>
       <c r="B9">
-        <v>949</v>
+        <v>967</v>
       </c>
       <c r="C9">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D9">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E9">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F9">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1172,13 +1172,13 @@
         <v>429660</v>
       </c>
       <c r="I9">
-        <v>220.9</v>
+        <v>225.1</v>
       </c>
       <c r="J9">
-        <v>18.6</v>
+        <v>17.7</v>
       </c>
       <c r="K9">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1268,7 +1268,7 @@
         <v>2</v>
       </c>
       <c r="F12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
         <v>6</v>
@@ -1323,150 +1323,150 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>410780</v>
+        <v>411480</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H14">
-        <v>4805</v>
+        <v>44749</v>
       </c>
       <c r="I14">
-        <v>145.7</v>
+        <v>147.5</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>411480</v>
+        <v>410780</v>
       </c>
       <c r="B15">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>2</v>
       </c>
-      <c r="D15">
-        <v>6</v>
-      </c>
-      <c r="E15">
-        <v>30</v>
-      </c>
       <c r="F15">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H15">
-        <v>44749</v>
+        <v>4805</v>
       </c>
       <c r="I15">
-        <v>145.3</v>
+        <v>145.7</v>
       </c>
       <c r="J15">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>412625</v>
+        <v>411810</v>
       </c>
       <c r="B16">
-        <v>141</v>
+        <v>11</v>
       </c>
       <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
         <v>10</v>
       </c>
-      <c r="D16">
-        <v>12</v>
-      </c>
-      <c r="E16">
-        <v>56</v>
-      </c>
-      <c r="F16">
-        <v>133</v>
-      </c>
       <c r="G16" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H16">
-        <v>128106</v>
+        <v>9549</v>
       </c>
       <c r="I16">
-        <v>110.1</v>
+        <v>115.2</v>
       </c>
       <c r="J16">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>411810</v>
+        <v>412625</v>
       </c>
       <c r="B17">
+        <v>145</v>
+      </c>
+      <c r="C17">
         <v>10</v>
       </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
       <c r="D17">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H17">
-        <v>9549</v>
+        <v>128106</v>
       </c>
       <c r="I17">
-        <v>104.7</v>
+        <v>113.2</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>411630</v>
+        <v>411360</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>3</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18">
-        <v>4057</v>
+        <v>4707</v>
       </c>
       <c r="I18">
-        <v>73.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>410210</v>
       </c>
       <c r="B19">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>26203</v>
       </c>
       <c r="I19">
-        <v>72.5</v>
+        <v>76.3</v>
       </c>
       <c r="J19">
         <v>3.8</v>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>411360</v>
+        <v>411630</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -1551,13 +1551,13 @@
         <v>3</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H20">
-        <v>4707</v>
+        <v>4057</v>
       </c>
       <c r="I20">
-        <v>63.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>411410</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1615,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F22">
         <v>17</v>
@@ -1627,7 +1627,7 @@
         <v>34521</v>
       </c>
       <c r="I22">
-        <v>52.1</v>
+        <v>57.9</v>
       </c>
       <c r="J22">
         <v>2.9</v>
@@ -1641,7 +1641,7 @@
         <v>411750</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23">
         <v>24</v>
@@ -1662,7 +1662,7 @@
         <v>48695</v>
       </c>
       <c r="I23">
-        <v>49.3</v>
+        <v>51.3</v>
       </c>
       <c r="J23">
         <v>2.1</v>
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1805,6 +1805,9 @@
         <v>36.9</v>
       </c>
       <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
         <v>0</v>
       </c>
     </row>
@@ -1917,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -2213,7 +2216,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2229,7 +2232,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2245,7 +2248,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2253,7 +2256,15 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2263,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C151"/>
+  <dimension ref="A1:C153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -3132,7 +3143,7 @@
         <v>46</v>
       </c>
       <c r="C79">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -3154,7 +3165,7 @@
         <v>47</v>
       </c>
       <c r="C81">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -3209,7 +3220,7 @@
         <v>46</v>
       </c>
       <c r="C86">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -3220,7 +3231,7 @@
         <v>47</v>
       </c>
       <c r="C87">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -3319,7 +3330,7 @@
         <v>46</v>
       </c>
       <c r="C96">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -3341,7 +3352,7 @@
         <v>47</v>
       </c>
       <c r="C98">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -3374,7 +3385,7 @@
         <v>46</v>
       </c>
       <c r="C101">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3385,7 +3396,7 @@
         <v>47</v>
       </c>
       <c r="C102">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -3440,7 +3451,7 @@
         <v>46</v>
       </c>
       <c r="C107">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:3">
@@ -3448,10 +3459,10 @@
         <v>29</v>
       </c>
       <c r="B108" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -3459,21 +3470,21 @@
         <v>29</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C109">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B110" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C110">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -3481,10 +3492,10 @@
         <v>30</v>
       </c>
       <c r="B111" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -3492,10 +3503,10 @@
         <v>30</v>
       </c>
       <c r="B112" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C112">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -3503,10 +3514,10 @@
         <v>30</v>
       </c>
       <c r="B113" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -3514,21 +3525,21 @@
         <v>30</v>
       </c>
       <c r="B114" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C114">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B115" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C115">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -3536,10 +3547,10 @@
         <v>31</v>
       </c>
       <c r="B116" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3547,7 +3558,7 @@
         <v>31</v>
       </c>
       <c r="B117" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C117">
         <v>8</v>
@@ -3558,21 +3569,21 @@
         <v>31</v>
       </c>
       <c r="B118" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C118">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B119" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C119">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -3580,10 +3591,10 @@
         <v>32</v>
       </c>
       <c r="B120" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C120">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3591,21 +3602,21 @@
         <v>32</v>
       </c>
       <c r="B121" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C121">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C122">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -3613,10 +3624,10 @@
         <v>33</v>
       </c>
       <c r="B123" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C123">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -3624,10 +3635,10 @@
         <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3635,21 +3646,21 @@
         <v>33</v>
       </c>
       <c r="B125" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C125">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B126" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C126">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -3657,7 +3668,7 @@
         <v>34</v>
       </c>
       <c r="B127" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C127">
         <v>12</v>
@@ -3668,32 +3679,32 @@
         <v>34</v>
       </c>
       <c r="B128" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B129" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C129">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B130" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C130">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3701,32 +3712,32 @@
         <v>35</v>
       </c>
       <c r="B131" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C131">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B132" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C132">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C133">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -3734,15 +3745,15 @@
         <v>36</v>
       </c>
       <c r="B134" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B135" t="s">
         <v>50</v>
@@ -3753,51 +3764,51 @@
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B136" t="s">
         <v>47</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B137" t="s">
         <v>48</v>
       </c>
       <c r="C137">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B138" t="s">
         <v>50</v>
       </c>
       <c r="C138">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B139" t="s">
         <v>47</v>
       </c>
       <c r="C139">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B140" t="s">
         <v>48</v>
@@ -3808,101 +3819,101 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B141" t="s">
         <v>50</v>
       </c>
       <c r="C141">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B142" t="s">
         <v>47</v>
       </c>
       <c r="C142">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B143" t="s">
         <v>48</v>
       </c>
       <c r="C143">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B144" t="s">
         <v>50</v>
       </c>
       <c r="C144">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B145" t="s">
         <v>47</v>
       </c>
       <c r="C145">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B146" t="s">
         <v>48</v>
       </c>
       <c r="C146">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B147" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C147">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C148">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B149" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C149">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -3910,20 +3921,42 @@
         <v>41</v>
       </c>
       <c r="B150" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B151" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152">
+        <v>42</v>
+      </c>
+      <c r="B152" t="s">
+        <v>50</v>
+      </c>
+      <c r="C152">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>42</v>
+      </c>
+      <c r="B153" t="s">
+        <v>48</v>
+      </c>
+      <c r="C153">
         <v>1</v>
       </c>
     </row>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -1113,28 +1113,28 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8">
-        <v>412530</v>
+        <v>412450</v>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8">
-        <v>5170</v>
+        <v>6463</v>
       </c>
       <c r="I8">
         <v>232.1</v>
@@ -1148,80 +1148,80 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9">
-        <v>411520</v>
+        <v>412530</v>
       </c>
       <c r="B9">
-        <v>967</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>285</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>877</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H9">
-        <v>429660</v>
+        <v>5170</v>
       </c>
       <c r="I9">
-        <v>225.1</v>
+        <v>232.1</v>
       </c>
       <c r="J9">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10">
-        <v>411640</v>
+        <v>411520</v>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>977</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>289</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>878</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H10">
-        <v>3669</v>
+        <v>429660</v>
       </c>
       <c r="I10">
-        <v>218</v>
+        <v>227.4</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>412450</v>
+        <v>411640</v>
       </c>
       <c r="B11">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1233,16 +1233,16 @@
         <v>3</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H11">
-        <v>6463</v>
+        <v>3669</v>
       </c>
       <c r="I11">
-        <v>216.6</v>
+        <v>218</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>30</v>
       </c>
       <c r="F14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
         <v>18</v>
@@ -1431,7 +1431,7 @@
         <v>412625</v>
       </c>
       <c r="B17">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -1443,7 +1443,7 @@
         <v>58</v>
       </c>
       <c r="F17">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G17" t="s">
         <v>31</v>
@@ -1452,13 +1452,13 @@
         <v>128106</v>
       </c>
       <c r="I17">
-        <v>113.2</v>
+        <v>114</v>
       </c>
       <c r="J17">
         <v>7.8</v>
       </c>
       <c r="K17">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1863,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
@@ -1920,7 +1920,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
@@ -2088,7 +2088,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2112,7 +2112,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2232,7 +2232,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -2248,7 +2248,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2264,7 +2264,15 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2846,7 +2854,7 @@
         <v>46</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -2868,7 +2876,7 @@
         <v>47</v>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -3110,7 +3118,7 @@
         <v>50</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -3231,7 +3239,7 @@
         <v>47</v>
       </c>
       <c r="C87">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -3756,10 +3764,10 @@
         <v>37</v>
       </c>
       <c r="B135" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C135">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3767,21 +3775,21 @@
         <v>37</v>
       </c>
       <c r="B136" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C136">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B137" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C137">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -3789,10 +3797,10 @@
         <v>38</v>
       </c>
       <c r="B138" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C138">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3800,21 +3808,21 @@
         <v>38</v>
       </c>
       <c r="B139" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C139">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B140" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C140">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3822,10 +3830,10 @@
         <v>39</v>
       </c>
       <c r="B141" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C141">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -3833,21 +3841,21 @@
         <v>39</v>
       </c>
       <c r="B142" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C142">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B143" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C143">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -3855,10 +3863,10 @@
         <v>40</v>
       </c>
       <c r="B144" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C144">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:3">
@@ -3866,21 +3874,21 @@
         <v>40</v>
       </c>
       <c r="B145" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C145">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B146" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C146">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -3888,10 +3896,10 @@
         <v>41</v>
       </c>
       <c r="B147" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -3899,10 +3907,10 @@
         <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C148">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -3910,21 +3918,21 @@
         <v>41</v>
       </c>
       <c r="B149" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B150" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C150">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -3932,10 +3940,10 @@
         <v>42</v>
       </c>
       <c r="B151" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -3943,21 +3951,21 @@
         <v>42</v>
       </c>
       <c r="B152" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C152">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B153" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
